--- a/Thesis_TSSP_NEW_M2_Results_10_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_10_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>74.1210 sec</t>
+          <t>72.3700 sec</t>
         </is>
       </c>
     </row>

--- a/Thesis_TSSP_NEW_M2_Results_10_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M2_Results_10_Scenarios.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
     </row>
@@ -537,12 +537,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 06:01</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
     </row>
@@ -616,27 +616,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:51</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
     </row>
@@ -653,17 +653,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 15:33</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -700,17 +700,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 07:14</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:09</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 13:13</t>
+          <t>4/5/2026 10:08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 15:20</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
     </row>
@@ -759,17 +759,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:34</t>
+          <t>4/5/2026 15:04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -801,17 +801,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:24</t>
+          <t>4/5/2026 10:20</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -833,32 +833,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:22</t>
+          <t>4/5/2026 14:09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 14:42</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 10:45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 10:28</t>
+          <t>4/5/2026 12:33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 11:39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 12:01</t>
+          <t>4/5/2026 15:01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 10:43</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 13:39</t>
+          <t>4/5/2026 08:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:39</t>
+          <t>4/5/2026 15:06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 10:24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 13:37</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 15:33</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 13:31</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:24</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:53</t>
+          <t>4/5/2026 11:21</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:43</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 10:18</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>436.00 min</t>
+          <t>433.90 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>45.35 min</t>
+          <t>43.56 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.90 min</t>
+          <t>87.10 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>119.00 min</t>
+          <t>108.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1027504 / 62787</t>
+          <t>1027513 / 62976</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>72.3700 sec</t>
+          <t>62.9860 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.8670 %</t>
+          <t>1.5915 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>46.19 min | 87.00 min</t>
+          <t>44.10 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>44.38 min | 86.00 min</t>
+          <t>42.81 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50.48 min | 92.00 min</t>
+          <t>50.05 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>46.52 min | 82.00 min</t>
+          <t>44.90 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>46.19 min | 78.00 min</t>
+          <t>44.05 min | 78.00 min</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>44.33 min | 84.00 min</t>
+          <t>42.00 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>40.95 min | 86.00 min</t>
+          <t>40.48 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>48.29 min | 89.00 min</t>
+          <t>45.24 min | 89.00 min</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>43.00 min | 119.00 min</t>
+          <t>40.95 min | 108.00 min</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>43.14 min | 86.00 min</t>
+          <t>41.00 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13.95</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="41">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9.300000000000001</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="42">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11.63</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="43">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13.95</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="44">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5.01</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="45">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.73</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="46">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.82</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="47">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>37.75</v>
+        <v>33.71</v>
       </c>
     </row>
     <row r="48">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25.16</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="49">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25.16</v>
+        <v>33.71</v>
       </c>
     </row>
   </sheetData>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:15</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2085,35 +2085,35 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>4/5/2026 09:19</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>4/5/2026 09:23</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:27</t>
-        </is>
-      </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -2145,35 +2145,35 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:41</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:06</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -2192,48 +2192,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:49</t>
+          <t>4/5/2026 06:51</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:09</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:32</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>5</v>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:07</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:30</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
       <c r="M8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2252,25 +2252,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 10:27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:34</t>
+          <t>4/5/2026 10:35</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:34</t>
+          <t>4/5/2026 10:35</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2385,29 +2385,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:41</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>4/5/2026 08:40</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>4/5/2026 08:42</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4/5/2026 08:46</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:42</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:46</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>13</v>
@@ -2625,35 +2625,35 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:19</t>
+          <t>4/5/2026 06:25</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:21</t>
+          <t>4/5/2026 06:27</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -2745,35 +2745,35 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M17" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N17" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -2805,35 +2805,35 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:41</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="N18" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -2972,16 +2972,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:42</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2994,26 +2994,26 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:37</t>
+          <t>4/5/2026 12:32</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -3032,48 +3032,48 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N22" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -3332,48 +3332,48 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>4/5/2026 09:12</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>4/5/2026 09:19</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>10</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:25</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L27" t="n">
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -3392,48 +3392,48 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:40</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:05</t>
         </is>
       </c>
       <c r="L28" t="n">
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N28" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
@@ -3465,35 +3465,35 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:09</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -3538,22 +3538,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -3705,16 +3705,16 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:49</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
         <v>23</v>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M34" t="n">
         <v>67</v>
@@ -3898,22 +3898,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -4005,35 +4005,35 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L38" t="n">
         <v>10</v>
       </c>
       <c r="M38" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -4065,35 +4065,35 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I39" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:36</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:44</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
         <v>6</v>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:39</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:47</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>10</v>
-      </c>
       <c r="M39" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N39" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
@@ -4292,48 +4292,48 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:14</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>18</v>
+      </c>
+      <c r="N43" t="n">
         <v>7</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:31</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:34</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M43" t="n">
-        <v>38</v>
-      </c>
-      <c r="N43" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -4532,48 +4532,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -4592,48 +4592,48 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>4/5/2026 09:16</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>4/5/2026 09:17</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:18</t>
-        </is>
-      </c>
       <c r="F48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L48" t="n">
         <v>10</v>
       </c>
       <c r="M48" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
@@ -4665,35 +4665,35 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:41</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M49" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -4725,35 +4725,35 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>4/5/2026 07:01</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>4/5/2026 07:03</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>4/5/2026 07:05</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:07</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L50" t="n">
         <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -4772,25 +4772,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -4798,22 +4798,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:00</t>
+          <t>4/5/2026 10:01</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:41</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="L51" t="n">
         <v>10</v>
       </c>
       <c r="M51" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N51" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
@@ -4832,29 +4832,29 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:05</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:12</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M52" t="n">
         <v>54</v>
@@ -5132,25 +5132,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:16</t>
+          <t>4/5/2026 06:17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
@@ -5265,35 +5265,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L59" t="n">
         <v>10</v>
       </c>
       <c r="M59" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N59" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60">
@@ -5325,35 +5325,35 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:46</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M60" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N60" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
@@ -5432,25 +5432,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:30</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:43</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:50</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -5458,22 +5458,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4/5/2026 09:52</t>
+          <t>4/5/2026 09:48</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>10</v>
       </c>
       <c r="M62" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="N62" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
@@ -5552,48 +5552,48 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:10</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
         <v>7</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:30</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:33</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>10</v>
-      </c>
       <c r="M64" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="N64" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -5672,25 +5672,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -5698,22 +5698,22 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M66" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -5805,35 +5805,35 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="N68" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -5852,48 +5852,48 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>4/5/2026 09:21</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>4/5/2026 09:24</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:27</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M69" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N69" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -5912,48 +5912,48 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:39</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>4/5/2026 07:42</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
           <t>4/5/2026 07:44</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:46</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:53</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:09</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M70" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N70" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -5972,48 +5972,48 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:03</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:10</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:33</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N71" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -6285,35 +6285,35 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>4/5/2026 13:27</t>
+          <t>4/5/2026 13:13</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="N76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6405,35 +6405,35 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:25</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:27</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79">
@@ -6512,48 +6512,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>4/5/2026 09:33</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>4/5/2026 09:35</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:37</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M80" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N80" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
@@ -6585,35 +6585,35 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M81" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N81" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -6812,48 +6812,48 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t>4/5/2026 08:57</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:04</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:04</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>4/5/2026 09:06</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>10</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:21</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="N85" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -7005,35 +7005,35 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:05</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:22</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="N88" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7065,35 +7065,35 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 13:36</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M89" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
@@ -7112,48 +7112,48 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
+          <t>4/5/2026 09:17</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>4/5/2026 09:18</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
       <c r="F90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M90" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N90" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91">
@@ -7185,35 +7185,35 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:41</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="L91" t="n">
         <v>10</v>
       </c>
       <c r="M91" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N91" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -7232,48 +7232,48 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:01</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:05</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:10</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:33</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M92" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93">
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:28</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>60</v>
@@ -7545,35 +7545,35 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:40</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:42</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="N97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7665,35 +7665,35 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:25</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L99" t="n">
         <v>4</v>
       </c>
       <c r="M99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
@@ -7725,29 +7725,29 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>4/5/2026 07:49</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
+          <t>4/5/2026 07:50</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
           <t>4/5/2026 07:51</t>
         </is>
       </c>
-      <c r="I100" t="n">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:55</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
         <v>1</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:51</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:55</t>
-        </is>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>12</v>
@@ -7798,22 +7798,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M101" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N101" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102">
@@ -7845,35 +7845,35 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M102" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N102" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -8072,48 +8072,48 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>4/5/2026 08:56</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>4/5/2026 09:05</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:14</t>
-        </is>
-      </c>
       <c r="F106" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M106" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N106" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
@@ -8145,35 +8145,35 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:49</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:51</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:59</t>
+          <t>4/5/2026 10:57</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:27</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M107" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
@@ -8372,16 +8372,16 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -8394,26 +8394,26 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M111" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N111" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
@@ -8432,48 +8432,48 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:38</t>
+          <t>4/5/2026 07:33</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:42</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M112" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N112" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113">
@@ -8492,48 +8492,48 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4/5/2026 06:53</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 06:58</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:06</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:09</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M113" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N113" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
@@ -8612,48 +8612,48 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>4/5/2026 08:27</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>4/5/2026 08:37</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:47</t>
-        </is>
-      </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M115" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="N115" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -8792,48 +8792,48 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:33</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4/5/2026 13:29</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="N118" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -8925,35 +8925,35 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:25</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:27</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N120" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121">
@@ -9058,22 +9058,22 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M122" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N122" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123">
@@ -9118,22 +9118,22 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M123" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N123" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124">
@@ -9152,48 +9152,48 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:01</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M124" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125">
@@ -9332,48 +9332,48 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
+          <t>4/5/2026 08:56</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:04</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
           <t>4/5/2026 09:06</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:14</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>10</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M127" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N127" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128">
@@ -9478,22 +9478,22 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -9512,48 +9512,48 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:57</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:59</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:00</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:07</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
         <v>1</v>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:05</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:07</t>
-        </is>
-      </c>
-      <c r="I130" t="n">
-        <v>7</v>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:14</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:21</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>7</v>
-      </c>
       <c r="M130" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="N130" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -9632,25 +9632,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
+          <t>4/5/2026 09:23</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
           <t>4/5/2026 09:25</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -9658,22 +9658,22 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M132" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N132" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
@@ -9692,48 +9692,48 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>4/5/2026 07:38</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
+          <t>4/5/2026 07:44</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
           <t>4/5/2026 07:45</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:46</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M133" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N133" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134">
@@ -9765,35 +9765,35 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4/5/2026 06:57</t>
+          <t>4/5/2026 07:03</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:06</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:09</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M134" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N134" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
@@ -9872,16 +9872,16 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:51</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -10052,48 +10052,48 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:32</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:51</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:31</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="N139" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -10172,48 +10172,48 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>4/5/2026 06:16</t>
+          <t>4/5/2026 06:18</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>4/5/2026 06:19</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:27</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N141" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142">
@@ -10292,48 +10292,48 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M143" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="N143" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144">
@@ -10352,25 +10352,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -10378,22 +10378,22 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:48</t>
         </is>
       </c>
       <c r="L144" t="n">
         <v>10</v>
       </c>
       <c r="M144" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N144" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145">
@@ -10412,48 +10412,48 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:41</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M145" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146">
@@ -10592,48 +10592,48 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M148" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="N148" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
@@ -10892,48 +10892,48 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
+          <t>4/5/2026 09:13</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>4</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
           <t>4/5/2026 09:19</t>
         </is>
       </c>
-      <c r="F153" t="n">
-        <v>10</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:24</t>
-        </is>
-      </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="L153" t="n">
         <v>10</v>
       </c>
       <c r="M153" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N153" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154">
@@ -10965,35 +10965,35 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:44</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:52</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:08</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M154" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N154" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="155">
@@ -11038,22 +11038,22 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:03</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:26</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="N155" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -11132,48 +11132,48 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
+          <t>4/5/2026 12:41</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:45</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:45</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:47</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
           <t>4/5/2026 12:51</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:55</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>10</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:02</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:04</t>
-        </is>
-      </c>
-      <c r="I157" t="n">
-        <v>7</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:14</t>
-        </is>
-      </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>4/5/2026 13:43</t>
+          <t>4/5/2026 13:20</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M157" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="N157" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -11338,22 +11338,22 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M160" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N160" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161">
@@ -11458,22 +11458,22 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M162" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N162" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163">
@@ -11552,48 +11552,48 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M164" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N164" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="165">
@@ -11612,48 +11612,48 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M165" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N165" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166">
@@ -11745,35 +11745,35 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M167" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="168">
@@ -11805,35 +11805,35 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>4/5/2026 12:37</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="N168" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -11852,48 +11852,48 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M169" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N169" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170">
@@ -11938,22 +11938,22 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M170" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -11985,35 +11985,35 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
+          <t>4/5/2026 09:54</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
           <t>4/5/2026 09:56</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:58</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>4/5/2026 10:08</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>4/5/2026 11:12</t>
+          <t>4/5/2026 11:01</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M171" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="N171" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172">
@@ -12045,35 +12045,35 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
+          <t>4/5/2026 13:01</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
           <t>4/5/2026 13:03</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:05</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>4/5/2026 13:22</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="N172" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -12152,48 +12152,48 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:33</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L174" t="n">
         <v>10</v>
       </c>
       <c r="M174" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N174" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="175">
@@ -12212,48 +12212,48 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:37</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:44</t>
+          <t>4/5/2026 07:43</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:45</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:50</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:06</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M175" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N175" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176">
@@ -12285,35 +12285,35 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>4/5/2026 07:04</t>
+          <t>4/5/2026 07:06</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>4/5/2026 07:06</t>
+          <t>4/5/2026 07:08</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:09</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="L176" t="n">
         <v>1</v>
       </c>
       <c r="M176" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N176" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
@@ -12705,35 +12705,35 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:25</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L183" t="n">
         <v>4</v>
       </c>
       <c r="M183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N183" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
@@ -12812,48 +12812,48 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:47</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L185" t="n">
         <v>10</v>
       </c>
       <c r="M185" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="N185" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="186">
@@ -12885,16 +12885,16 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M186" t="n">
         <v>43</v>
@@ -13112,48 +13112,48 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:10</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t>4/5/2026 09:13</t>
         </is>
       </c>
-      <c r="F190" t="n">
-        <v>10</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:21</t>
-        </is>
-      </c>
-      <c r="I190" t="n">
-        <v>6</v>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:31</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:34</t>
-        </is>
-      </c>
       <c r="L190" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M190" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N190" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191">
@@ -13258,22 +13258,22 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:11</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M192" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N192" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -13412,48 +13412,48 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
+          <t>4/5/2026 09:18</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>2</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
           <t>4/5/2026 09:27</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>7</v>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:37</t>
-        </is>
-      </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M195" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N195" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="196">
@@ -13472,25 +13472,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:21</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
+          <t>4/5/2026 07:30</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>2</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>4/5/2026 07:36</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
           <t>4/5/2026 07:38</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>10</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:44</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:04</t>
         </is>
       </c>
       <c r="L196" t="n">
         <v>10</v>
       </c>
       <c r="M196" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="N196" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="197">
@@ -13545,35 +13545,35 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>4/5/2026 07:05</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>4/5/2026 07:07</t>
+          <t>4/5/2026 07:06</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="L197" t="n">
         <v>2</v>
       </c>
       <c r="M197" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -13952,48 +13952,48 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:16</t>
+          <t>4/5/2026 06:17</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:26</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:28</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:24</t>
+          <t>4/5/2026 06:29</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:26</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N204" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205">
@@ -14072,48 +14072,48 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I206" t="n">
+        <v>4</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:43</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:52</t>
+        </is>
+      </c>
+      <c r="L206" t="n">
         <v>7</v>
       </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:47</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:56</t>
-        </is>
-      </c>
-      <c r="L206" t="n">
-        <v>10</v>
-      </c>
       <c r="M206" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N206" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="207">
@@ -14145,35 +14145,35 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I207" t="n">
+        <v>7</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:36</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:44</t>
+        </is>
+      </c>
+      <c r="L207" t="n">
         <v>6</v>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:39</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:47</t>
-        </is>
-      </c>
-      <c r="L207" t="n">
-        <v>10</v>
-      </c>
       <c r="M207" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N207" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="208">
@@ -14372,48 +14372,48 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:03</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:05</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:10</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t>4/5/2026 09:13</t>
         </is>
       </c>
-      <c r="F211" t="n">
-        <v>10</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:19</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:21</t>
-        </is>
-      </c>
-      <c r="I211" t="n">
-        <v>6</v>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:31</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:34</t>
-        </is>
-      </c>
       <c r="L211" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M211" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N211" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
